--- a/비초소_태스크_리스트.xlsx
+++ b/비초소_태스크_리스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shes4\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65A2481-0B75-45DF-9547-6BA05E5A30FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA16EB-A939-4BBD-9B1E-382335CE7829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="155">
   <si>
     <t>경비원명</t>
   </si>
@@ -889,7 +889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1009,9 +1009,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -1656,13 +1653,13 @@
     <row r="5" spans="1:6">
       <c r="A5" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1752,13 +1749,13 @@
     <row r="13" spans="1:6">
       <c r="A13" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1776,13 +1773,13 @@
     <row r="15" spans="1:6">
       <c r="A15" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2338,7 +2335,7 @@
       <c r="C2" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="51" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2346,7 +2343,7 @@
       <c r="A3" s="18"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
-      <c r="D3" s="46"/>
+      <c r="D3" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2550,7 +2547,7 @@
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="48" t="s">
         <v>102</v>
       </c>
       <c r="C13" s="9">
@@ -2565,7 +2562,7 @@
       <c r="A14" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="48" t="s">
         <v>101</v>
       </c>
       <c r="C14" s="9">
@@ -2580,7 +2577,7 @@
       <c r="A15" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="48" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="9">
@@ -2595,7 +2592,7 @@
       <c r="A16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="48" t="s">
         <v>104</v>
       </c>
       <c r="C16" s="9">
@@ -2610,7 +2607,7 @@
       <c r="A17" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="48" t="s">
         <v>105</v>
       </c>
       <c r="C17" s="9">
@@ -2964,7 +2961,7 @@
       <c r="C1" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="50" t="s">
         <v>72</v>
       </c>
       <c r="E1" s="36" t="s">
@@ -2988,7 +2985,7 @@
       <c r="K1" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="43">
+      <c r="L1" s="42">
         <v>46223</v>
       </c>
       <c r="M1" s="33" t="str">
@@ -3056,7 +3053,7 @@
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
-      <c r="L2" s="50" t="s">
+      <c r="L2" s="49" t="s">
         <v>131</v>
       </c>
       <c r="M2" s="33" t="str">
@@ -3153,7 +3150,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
-      <c r="L4" s="50" t="s">
+      <c r="L4" s="49" t="s">
         <v>132</v>
       </c>
       <c r="M4" s="33" t="str">
@@ -3162,7 +3159,7 @@
       </c>
       <c r="N4" s="33" t="str">
         <f t="array" ref="N4">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M4))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <v>휴-3B</v>
       </c>
       <c r="P4" s="29" t="s">
         <v>71</v>
@@ -3474,7 +3471,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
-      <c r="L10" s="50" t="s">
+      <c r="L10" s="49" t="s">
         <v>133</v>
       </c>
       <c r="M10" s="33" t="str">
@@ -3511,11 +3508,13 @@
       <c r="A11" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="E11" s="30" t="s">
         <v>145</v>
       </c>
@@ -3540,11 +3539,13 @@
       <c r="P11" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="Q11" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="T11" s="30" t="s">
         <v>145</v>
       </c>
@@ -3581,7 +3582,7 @@
       </c>
       <c r="N12" s="33" t="str">
         <f t="array" ref="N12">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M12))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v>휴-3A</v>
       </c>
       <c r="P12" s="29" t="s">
         <v>66</v>
@@ -3601,13 +3602,11 @@
       <c r="A13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="B13" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
         <v>146</v>
@@ -3632,13 +3631,11 @@
       <c r="P13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="S13" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="Q13" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="30" t="s">
         <v>146</v>
@@ -3681,7 +3678,7 @@
       </c>
       <c r="N14" s="33" t="str">
         <f t="array" ref="N14">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M14))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v>휴-3A</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>87</v>
@@ -3953,26 +3950,26 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47" t="s">
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="50" t="s">
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="49" t="s">
         <v>134</v>
       </c>
       <c r="M21" s="33" t="str">
@@ -3983,41 +3980,41 @@
         <f t="array" ref="N21">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M21))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>휴-3A</v>
       </c>
-      <c r="P21" s="47" t="s">
+      <c r="P21" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47" t="s">
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47" t="s">
+      <c r="T21" s="46"/>
+      <c r="U21" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="V21" s="47" t="s">
+      <c r="V21" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="46"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="50" t="s">
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="49" t="s">
         <v>135</v>
       </c>
       <c r="M22" s="33" t="str">
@@ -4028,44 +4025,44 @@
         <f t="array" ref="N22">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M22))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>소-1</v>
       </c>
-      <c r="P22" s="47" t="s">
+      <c r="P22" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47" t="s">
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="S22" s="47" t="s">
+      <c r="S22" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="T22" s="47"/>
-      <c r="U22" s="47" t="s">
+      <c r="T22" s="46"/>
+      <c r="U22" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="V22" s="47" t="s">
+      <c r="V22" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="W22" s="47"/>
-      <c r="X22" s="47"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="47"/>
+      <c r="W22" s="46"/>
+      <c r="X22" s="46"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="46"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47" t="s">
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
       <c r="L23" s="31" t="s">
         <v>136</v>
       </c>
@@ -4077,46 +4074,46 @@
         <f t="array" ref="N23">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M23))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>등-1</v>
       </c>
-      <c r="P23" s="47" t="s">
+      <c r="P23" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47" t="s">
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="T23" s="47" t="s">
+      <c r="T23" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47" t="s">
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47" t="s">
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47" t="s">
+      <c r="F24" s="46"/>
+      <c r="G24" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
       <c r="L24" s="31" t="s">
         <v>137</v>
       </c>
@@ -4128,40 +4125,40 @@
         <f t="array" ref="N24">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M24))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>보-1</v>
       </c>
-      <c r="P24" s="47" t="s">
+      <c r="P24" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="Q24" s="47" t="s">
+      <c r="Q24" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="R24" s="47"/>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47" t="s">
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="U24" s="47"/>
-      <c r="V24" s="47" t="s">
+      <c r="U24" s="46"/>
+      <c r="V24" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="W24" s="47"/>
-      <c r="X24" s="47"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
       <c r="L25" s="31" t="s">
         <v>138</v>
       </c>
@@ -4173,40 +4170,40 @@
         <f t="array" ref="N25">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M25))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>휴-1B</v>
       </c>
-      <c r="P25" s="47" t="s">
+      <c r="P25" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47" t="s">
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="47" t="s">
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="V25" s="47"/>
-      <c r="W25" s="47" t="s">
+      <c r="V25" s="46"/>
+      <c r="W25" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="X25" s="47"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="47"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
       <c r="M26" s="33" t="str">
         <f t="array" ref="M26">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
@@ -4215,34 +4212,34 @@
         <f t="array" ref="N26">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>휴-2B</v>
       </c>
-      <c r="P26" s="47" t="s">
+      <c r="P26" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="47"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="47"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="47"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
       <c r="M27" s="33" t="str">
         <f t="array" ref="M27">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
@@ -4251,34 +4248,34 @@
         <f t="array" ref="N27">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>게-1</v>
       </c>
-      <c r="P27" s="47" t="s">
+      <c r="P27" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
       <c r="M28" s="33" t="str">
         <f t="array" ref="M28">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M28))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
@@ -4290,33 +4287,33 @@
       <c r="P28" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="42"/>
-      <c r="W28" s="42"/>
-      <c r="X28" s="42"/>
-      <c r="Y28" s="42"/>
-      <c r="Z28" s="42"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44" t="s">
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
       <c r="M29" s="33" t="str">
         <f t="array" ref="M29">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M29))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
@@ -4328,31 +4325,31 @@
       <c r="P29" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="42"/>
-      <c r="W29" s="42"/>
-      <c r="X29" s="42"/>
-      <c r="Y29" s="42"/>
-      <c r="Z29" s="42"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="M30" s="33" t="str">
         <f t="array" ref="M30">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M30))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
@@ -4364,57 +4361,57 @@
       <c r="P30" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
-      <c r="Z30" s="42"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
     </row>
     <row r="31" spans="1:26">
       <c r="B31" s="31">
-        <f>SUM(B2:B27)</f>
-        <v>0</v>
+        <f>COUNTA(B2:B30)</f>
+        <v>6</v>
       </c>
       <c r="C31" s="31">
-        <f>SUM(C2:C27)</f>
-        <v>0</v>
+        <f t="shared" ref="C31:K31" si="0">COUNTA(C2:C30)</f>
+        <v>6</v>
       </c>
       <c r="D31" s="31">
-        <f>SUM(D2:D27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="E31" s="31">
-        <f>SUM(E2:E27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="F31" s="31">
-        <f>SUM(F2:F27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G31" s="31">
-        <f>SUM(G2:G27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="H31" s="31">
-        <f>SUM(H2:H27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="I31" s="31">
-        <f>SUM(I2:I27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="J31" s="31">
-        <f>SUM(J2:J27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="K31" s="31">
-        <f>SUM(K2:K27)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="M31" s="33" t="str">
         <f t="array" ref="M31">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M31))-1)/ROWS($A$2:$A$30))+1),"")</f>
@@ -4425,44 +4422,44 @@
         <v>주-1</v>
       </c>
       <c r="Q31" s="31">
-        <f t="shared" ref="Q31:Z31" si="0">SUM(Q1:Q27)</f>
-        <v>0</v>
+        <f>COUNTA(Q2:Q30)</f>
+        <v>5</v>
       </c>
       <c r="R31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="R31" si="1">COUNTA(R2:R30)</f>
+        <v>8</v>
       </c>
       <c r="S31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="S31" si="2">COUNTA(S2:S30)</f>
+        <v>11</v>
       </c>
       <c r="T31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="T31" si="3">COUNTA(T2:T30)</f>
+        <v>9</v>
       </c>
       <c r="U31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="U31" si="4">COUNTA(U2:U30)</f>
+        <v>9</v>
       </c>
       <c r="V31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="V31" si="5">COUNTA(V2:V30)</f>
+        <v>14</v>
       </c>
       <c r="W31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="W31" si="6">COUNTA(W2:W30)</f>
+        <v>8</v>
       </c>
       <c r="X31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="X31" si="7">COUNTA(X2:X30)</f>
+        <v>3</v>
       </c>
       <c r="Y31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="Y31" si="8">COUNTA(Y2:Y30)</f>
+        <v>3</v>
       </c>
       <c r="Z31" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="Z31" si="9">COUNTA(Z2:Z30)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:26">
@@ -4475,8 +4472,8 @@
         <v>휴-1A</v>
       </c>
     </row>
-    <row r="33" spans="5:26">
-      <c r="E33" s="45"/>
+    <row r="33" spans="5:14">
+      <c r="E33" s="44"/>
       <c r="M33" s="33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4485,21 +4482,8 @@
         <f t="array" ref="N33">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>휴-2A</v>
       </c>
-      <c r="P33" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="42"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="42"/>
-      <c r="W33" s="42"/>
-      <c r="X33" s="42"/>
-      <c r="Y33" s="42"/>
-      <c r="Z33" s="42"/>
-    </row>
-    <row r="34" spans="5:26">
+    </row>
+    <row r="34" spans="5:14">
       <c r="M34" s="33" t="str">
         <f t="array" ref="M34">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M34))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4508,21 +4492,8 @@
         <f t="array" ref="N34">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M34))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>게-1</v>
       </c>
-      <c r="P34" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="42"/>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
-      <c r="W34" s="42"/>
-      <c r="X34" s="42"/>
-      <c r="Y34" s="42"/>
-      <c r="Z34" s="42"/>
-    </row>
-    <row r="35" spans="5:26">
+    </row>
+    <row r="35" spans="5:14">
       <c r="M35" s="33" t="str">
         <f t="array" ref="M35">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M35))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4531,21 +4502,8 @@
         <f t="array" ref="N35">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M35))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>주-5</v>
       </c>
-      <c r="P35" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="42"/>
-      <c r="U35" s="42"/>
-      <c r="V35" s="42"/>
-      <c r="W35" s="42"/>
-      <c r="X35" s="42"/>
-      <c r="Y35" s="42"/>
-      <c r="Z35" s="42"/>
-    </row>
-    <row r="36" spans="5:26">
+    </row>
+    <row r="36" spans="5:14">
       <c r="M36" s="33" t="str">
         <f t="array" ref="M36">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M36))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4554,21 +4512,8 @@
         <f t="array" ref="N36">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M36))-1,ROWS($A$2:$A$30))+1),"")</f>
         <v>휴-3A</v>
       </c>
-      <c r="P36" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="42"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="42"/>
-      <c r="W36" s="42"/>
-      <c r="X36" s="42"/>
-      <c r="Y36" s="42"/>
-      <c r="Z36" s="42"/>
-    </row>
-    <row r="37" spans="5:26">
+    </row>
+    <row r="37" spans="5:14">
       <c r="M37" s="33" t="str">
         <f t="array" ref="M37">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M37))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4578,7 +4523,7 @@
         <v>소-1</v>
       </c>
     </row>
-    <row r="38" spans="5:26">
+    <row r="38" spans="5:14">
       <c r="M38" s="33" t="str">
         <f t="array" ref="M38">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M38))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4588,7 +4533,7 @@
         <v>맘-1</v>
       </c>
     </row>
-    <row r="39" spans="5:26">
+    <row r="39" spans="5:14">
       <c r="M39" s="33" t="str">
         <f t="array" ref="M39">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M39))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4598,7 +4543,7 @@
         <v>G-3</v>
       </c>
     </row>
-    <row r="40" spans="5:26">
+    <row r="40" spans="5:14">
       <c r="M40" s="33" t="str">
         <f t="array" ref="M40">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M40))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4608,7 +4553,7 @@
         <v>푸-1</v>
       </c>
     </row>
-    <row r="41" spans="5:26">
+    <row r="41" spans="5:14">
       <c r="M41" s="33" t="str">
         <f t="array" ref="M41">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M41))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4618,7 +4563,7 @@
         <v>주-3</v>
       </c>
     </row>
-    <row r="42" spans="5:26">
+    <row r="42" spans="5:14">
       <c r="M42" s="33" t="str">
         <f t="array" ref="M42">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M42))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
@@ -4628,7 +4573,7 @@
         <v>보-1</v>
       </c>
     </row>
-    <row r="43" spans="5:26">
+    <row r="43" spans="5:14">
       <c r="M43" s="33" t="str">
         <f t="array" ref="M43">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M43))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>
@@ -4638,7 +4583,7 @@
         <v>휴-1B</v>
       </c>
     </row>
-    <row r="44" spans="5:26">
+    <row r="44" spans="5:14">
       <c r="M44" s="33" t="str">
         <f t="array" ref="M44">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M44))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>
@@ -4648,7 +4593,7 @@
         <v>휴-2B</v>
       </c>
     </row>
-    <row r="45" spans="5:26">
+    <row r="45" spans="5:14">
       <c r="M45" s="33" t="str">
         <f t="array" ref="M45">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M45))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>
@@ -4658,7 +4603,7 @@
         <v>점-1</v>
       </c>
     </row>
-    <row r="46" spans="5:26">
+    <row r="46" spans="5:14">
       <c r="M46" s="33" t="str">
         <f t="array" ref="M46">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M46))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>
@@ -4668,7 +4613,7 @@
         <v>휴-3B</v>
       </c>
     </row>
-    <row r="47" spans="5:26">
+    <row r="47" spans="5:14">
       <c r="M47" s="33" t="str">
         <f t="array" ref="M47">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M47))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>
@@ -4678,7 +4623,7 @@
         <v>G-1</v>
       </c>
     </row>
-    <row r="48" spans="5:26">
+    <row r="48" spans="5:14">
       <c r="M48" s="33" t="str">
         <f t="array" ref="M48">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M48))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>김민겸</v>

--- a/비초소_태스크_리스트.xlsx
+++ b/비초소_태스크_리스트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shes4\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA16EB-A939-4BBD-9B1E-382335CE7829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF337068-7C2F-475B-AC88-B325E8F6EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="25820" windowHeight="15500" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="배치" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
   <si>
     <t>경비원명</t>
   </si>
@@ -236,249 +236,249 @@
   </si>
   <si>
     <t>이근재</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-3C</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴게(자정)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-1B</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-3A</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>보-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>이학근</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>B</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-3B</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-2B</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>자-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체-전일</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체-오전</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체-오후</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체-남</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>이춘도</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>게-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>점-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>소-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-1A</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>휴-2A</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>재-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>유복현</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>신운기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>김민겸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>정창화</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>박동원</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>이동철</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>여연동</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>분담표</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(11)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(07)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(14)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(20)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(21)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>기준표</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체근무</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대체-임시1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>등-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>등원안내</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>맘-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>맘개방</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>푸-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>푸른개방</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>물-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>물오뚜기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>청-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>대청소</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-2</t>
   </si>
   <si>
     <t>G-2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-3</t>
   </si>
   <si>
     <t>G-3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-소등</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-확인2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>G-확인1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>등-1</t>
@@ -494,98 +494,97 @@
   </si>
   <si>
     <t>(07)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(11)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(21)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(14)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(20)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>동→서→북</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(일)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(월),(목)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(개방)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(소등)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(안내)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>춘</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>근</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>학</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>창</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>운</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>복</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>민</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>동</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>연</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>원</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>북초소</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>게시-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>주-5</t>
+  </si>
+  <si>
+    <t>휴-3C</t>
   </si>
 </sst>
 </file>
@@ -600,6 +599,14 @@
   <fonts count="25">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -768,14 +775,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
@@ -885,7 +884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -893,14 +892,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -917,86 +913,116 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1005,40 +1031,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1587,14 +1586,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="25" customWidth="1"/>
@@ -1617,94 +1616,94 @@
     <row r="2" spans="1:6">
       <c r="A2" s="26">
         <f t="shared" ref="A2:A32" si="0">IF(OR(C2="소-1",C2="휴-3B",C2="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>37</v>
@@ -1713,10 +1712,10 @@
     <row r="10" spans="1:6">
       <c r="A10" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>38</v>
@@ -1725,10 +1724,10 @@
     <row r="11" spans="1:6">
       <c r="A11" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>40</v>
@@ -1737,566 +1736,542 @@
     <row r="12" spans="1:6">
       <c r="A12" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="26">
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B19" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" s="28"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="28"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B22" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B27" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="26">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="26">
         <f t="shared" si="0"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B32" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="26">
-        <f t="shared" ref="A33:A57" si="1">IF(OR(C33="소-1",C33="휴-3B",C33="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46223</v>
+        <f t="shared" ref="A33:A55" si="1">IF(OR(C33="소-1",C33="휴-3B",C33="휴-3C"),$F$16+1,$F$16)</f>
+        <v>46225</v>
       </c>
       <c r="B33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B34" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="26">
         <f t="shared" si="1"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="26">
         <f t="shared" ref="A43:A44" si="2">IF(OR(C43="소-1",C43="휴-3B",C43="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="26">
         <f t="shared" si="2"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B44" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B45" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="26">
         <f t="shared" si="1"/>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="26">
         <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="26">
-        <f t="shared" si="1"/>
-        <v>46224</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="26">
-        <f t="shared" si="1"/>
-        <v>46223</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C57" s="27" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C51" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2327,7 +2302,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="18">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>95</v>
@@ -2336,17 +2311,17 @@
         <v>152</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="18"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
-      <c r="D3" s="45"/>
+      <c r="D3" s="44"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2547,7 +2522,7 @@
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>102</v>
       </c>
       <c r="C13" s="9">
@@ -2562,7 +2537,7 @@
       <c r="A14" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="47" t="s">
         <v>101</v>
       </c>
       <c r="C14" s="9">
@@ -2577,7 +2552,7 @@
       <c r="A15" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="47" t="s">
         <v>103</v>
       </c>
       <c r="C15" s="9">
@@ -2592,7 +2567,7 @@
       <c r="A16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="47" t="s">
         <v>104</v>
       </c>
       <c r="C16" s="9">
@@ -2607,7 +2582,7 @@
       <c r="A17" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="47" t="s">
         <v>105</v>
       </c>
       <c r="C17" s="9">
@@ -2926,7 +2901,7 @@
       <c r="C40"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2944,7 +2919,7 @@
     <col min="7" max="8" width="5.5546875" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.6640625" style="31" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="5.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="31" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="8.88671875" style="33"/>
     <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -2961,7 +2936,7 @@
       <c r="C1" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>72</v>
       </c>
       <c r="E1" s="36" t="s">
@@ -2985,8 +2960,8 @@
       <c r="K1" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="42">
-        <v>46223</v>
+      <c r="L1" s="50">
+        <v>46225</v>
       </c>
       <c r="M1" s="33" t="str">
         <f t="array" ref="M1">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M1))-1)/ROWS($A$2:$A$30))+1),"")</f>
@@ -2994,7 +2969,7 @@
       </c>
       <c r="N1" s="33" t="str">
         <f t="array" ref="N1">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M1))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <v>연-1</v>
       </c>
       <c r="O1" s="39" t="s">
         <v>106</v>
@@ -3053,16 +3028,16 @@
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
-      <c r="L2" s="49" t="s">
+      <c r="L2" s="48" t="s">
         <v>131</v>
       </c>
       <c r="M2" s="33" t="str">
         <f t="array" ref="M2">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M2))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이춘도</v>
+        <v>이근재</v>
       </c>
       <c r="N2" s="33" t="str">
         <f t="array" ref="N2">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M2))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <v>주-1</v>
       </c>
       <c r="P2" s="34" t="s">
         <v>83</v>
@@ -3088,10 +3063,10 @@
       <c r="A3" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30" t="s">
         <v>145</v>
@@ -3108,11 +3083,11 @@
       <c r="K3" s="30"/>
       <c r="M3" s="33" t="str">
         <f t="array" ref="M3">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M3))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이춘도</v>
+        <v>이근재</v>
       </c>
       <c r="N3" s="33" t="str">
         <f t="array" ref="N3">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M3))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
+        <v>휴-1A</v>
       </c>
       <c r="P3" s="34" t="s">
         <v>88</v>
@@ -3150,16 +3125,16 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
-      <c r="L4" s="49" t="s">
+      <c r="L4" s="48" t="s">
         <v>132</v>
       </c>
       <c r="M4" s="33" t="str">
         <f t="array" ref="M4">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M4))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이춘도</v>
+        <v>이근재</v>
       </c>
       <c r="N4" s="33" t="str">
         <f t="array" ref="N4">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M4))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v>휴-2A</v>
       </c>
       <c r="P4" s="29" t="s">
         <v>71</v>
@@ -3186,10 +3161,10 @@
         <v>68</v>
       </c>
       <c r="B5" s="30"/>
-      <c r="C5" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30" t="s">
         <v>146</v>
@@ -3207,11 +3182,11 @@
       </c>
       <c r="M5" s="33" t="str">
         <f t="array" ref="M5">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M5))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이춘도</v>
+        <v>이근재</v>
       </c>
       <c r="N5" s="33" t="str">
         <f t="array" ref="N5">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M5))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <v>게-1</v>
       </c>
       <c r="P5" s="29" t="s">
         <v>68</v>
@@ -3243,10 +3218,10 @@
       <c r="A6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="D6" s="30"/>
       <c r="E6" s="30" t="s">
         <v>145</v>
@@ -3263,11 +3238,11 @@
       <c r="K6" s="30"/>
       <c r="M6" s="33" t="str">
         <f t="array" ref="M6">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M6))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이춘도</v>
+        <v>이근재</v>
       </c>
       <c r="N6" s="33" t="str">
         <f t="array" ref="N6">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M6))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>보-1</v>
+        <v>휴-3A</v>
       </c>
       <c r="P6" s="29" t="s">
         <v>89</v>
@@ -3296,10 +3271,10 @@
         <v>76</v>
       </c>
       <c r="B7" s="30"/>
-      <c r="C7" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30" t="s">
         <v>146</v>
@@ -3321,7 +3296,7 @@
       </c>
       <c r="N7" s="33" t="str">
         <f t="array" ref="N7">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M7))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
+        <v>소-1</v>
       </c>
       <c r="P7" s="29" t="s">
         <v>76</v>
@@ -3354,10 +3329,10 @@
         <v>86</v>
       </c>
       <c r="B8" s="30"/>
-      <c r="C8" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="E8" s="30" t="s">
         <v>145</v>
       </c>
@@ -3371,7 +3346,7 @@
       <c r="K8" s="30"/>
       <c r="M8" s="33" t="str">
         <f t="array" ref="M8">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M8))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <v>이학근</v>
       </c>
       <c r="N8" s="33" t="str">
         <f t="array" ref="N8">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M8))-1,ROWS($A$2:$A$30))+1),"")</f>
@@ -3403,10 +3378,10 @@
       <c r="A9" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30" t="s">
@@ -3421,7 +3396,7 @@
       <c r="K9" s="30"/>
       <c r="M9" s="33" t="str">
         <f t="array" ref="M9">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M9))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <v>이학근</v>
       </c>
       <c r="N9" s="33" t="str">
         <f t="array" ref="N9">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M9))-1,ROWS($A$2:$A$30))+1),"")</f>
@@ -3454,9 +3429,7 @@
         <v>100</v>
       </c>
       <c r="B10" s="30"/>
-      <c r="C10" s="30" t="s">
-        <v>143</v>
-      </c>
+      <c r="C10" s="30"/>
       <c r="D10" s="30" t="s">
         <v>144</v>
       </c>
@@ -3471,12 +3444,12 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
-      <c r="L10" s="49" t="s">
+      <c r="L10" s="48" t="s">
         <v>133</v>
       </c>
       <c r="M10" s="33" t="str">
         <f t="array" ref="M10">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M10))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <v>이학근</v>
       </c>
       <c r="N10" s="33" t="str">
         <f t="array" ref="N10">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M10))-1,ROWS($A$2:$A$30))+1),"")</f>
@@ -3512,9 +3485,7 @@
       <c r="C11" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="D11" s="30"/>
       <c r="E11" s="30" t="s">
         <v>145</v>
       </c>
@@ -3530,7 +3501,7 @@
       <c r="K11" s="30"/>
       <c r="M11" s="33" t="str">
         <f t="array" ref="M11">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M11))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <v>이학근</v>
       </c>
       <c r="N11" s="33" t="str">
         <f t="array" ref="N11">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M11))-1,ROWS($A$2:$A$30))+1),"")</f>
@@ -3578,11 +3549,11 @@
       </c>
       <c r="M12" s="33" t="str">
         <f t="array" ref="M12">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M12))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <v>이학근</v>
       </c>
       <c r="N12" s="33" t="str">
         <f t="array" ref="N12">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M12))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <v>휴-3B</v>
       </c>
       <c r="P12" s="29" t="s">
         <v>66</v>
@@ -3602,11 +3573,11 @@
       <c r="A13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="30" t="s">
-        <v>142</v>
-      </c>
+      <c r="B13" s="30"/>
       <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="D13" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
         <v>146</v>
@@ -3626,7 +3597,7 @@
       </c>
       <c r="N13" s="33" t="str">
         <f t="array" ref="N13">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M13))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
+        <v>주-3</v>
       </c>
       <c r="P13" s="29" t="s">
         <v>75</v>
@@ -3657,10 +3628,10 @@
         <v>87</v>
       </c>
       <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="C14" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="30"/>
       <c r="E14" s="30" t="s">
         <v>145</v>
       </c>
@@ -3678,7 +3649,7 @@
       </c>
       <c r="N14" s="33" t="str">
         <f t="array" ref="N14">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M14))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <v>자-1</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>87</v>
@@ -3721,11 +3692,11 @@
       </c>
       <c r="M15" s="33" t="str">
         <f t="array" ref="M15">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M15))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <v>정창화</v>
       </c>
       <c r="N15" s="33" t="str">
         <f t="array" ref="N15">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M15))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
+        <v>주-1</v>
       </c>
       <c r="P15" s="29" t="s">
         <v>109</v>
@@ -3761,11 +3732,11 @@
       <c r="K16" s="30"/>
       <c r="M16" s="33" t="str">
         <f t="array" ref="M16">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M16))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <v>정창화</v>
       </c>
       <c r="N16" s="33" t="str">
         <f t="array" ref="N16">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M16))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>연-2</v>
+        <v>휴-1A</v>
       </c>
       <c r="P16" s="29" t="s">
         <v>111</v>
@@ -3805,7 +3776,7 @@
       </c>
       <c r="N17" s="33" t="str">
         <f t="array" ref="N17">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M17))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
+        <v>휴-2A</v>
       </c>
       <c r="P17" s="29" t="s">
         <v>119</v>
@@ -3845,7 +3816,7 @@
       </c>
       <c r="N18" s="33" t="str">
         <f t="array" ref="N18">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M18))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <v>점-1</v>
       </c>
       <c r="P18" s="29" t="s">
         <v>120</v>
@@ -3888,7 +3859,7 @@
       </c>
       <c r="N19" s="33" t="str">
         <f t="array" ref="N19">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M19))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <v>휴-3A</v>
       </c>
       <c r="P19" s="29" t="s">
         <v>122</v>
@@ -3931,7 +3902,7 @@
       </c>
       <c r="N20" s="33" t="str">
         <f t="array" ref="N20">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M20))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>점-1</v>
+        <v>소-1</v>
       </c>
       <c r="P20" s="29" t="s">
         <v>113</v>
@@ -3950,26 +3921,26 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="49" t="s">
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="48" t="s">
         <v>134</v>
       </c>
       <c r="M21" s="33" t="str">
@@ -3978,187 +3949,181 @@
       </c>
       <c r="N21" s="33" t="str">
         <f t="array" ref="N21">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M21))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
-      </c>
-      <c r="P21" s="46" t="s">
+        <v>등-1</v>
+      </c>
+      <c r="P21" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46" t="s">
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46" t="s">
+      <c r="T21" s="45"/>
+      <c r="U21" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="V21" s="46" t="s">
+      <c r="V21" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="45"/>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="45"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="49" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="48" t="s">
         <v>135</v>
       </c>
       <c r="M22" s="33" t="str">
         <f t="array" ref="M22">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M22))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <v>신운기</v>
       </c>
       <c r="N22" s="33" t="str">
         <f t="array" ref="N22">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M22))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
-      </c>
-      <c r="P22" s="46" t="s">
+        <v>휴-1B</v>
+      </c>
+      <c r="P22" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46" t="s">
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="S22" s="46" t="s">
+      <c r="S22" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="T22" s="46"/>
-      <c r="U22" s="46" t="s">
+      <c r="T22" s="45"/>
+      <c r="U22" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="V22" s="46" t="s">
+      <c r="V22" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="W22" s="46"/>
-      <c r="X22" s="46"/>
-      <c r="Y22" s="46"/>
-      <c r="Z22" s="46"/>
+      <c r="W22" s="45"/>
+      <c r="X22" s="45"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="45"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
       <c r="L23" s="31" t="s">
         <v>136</v>
       </c>
       <c r="M23" s="33" t="str">
         <f t="array" ref="M23">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M23))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <v>신운기</v>
       </c>
       <c r="N23" s="33" t="str">
         <f t="array" ref="N23">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M23))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>등-1</v>
-      </c>
-      <c r="P23" s="46" t="s">
+        <v>휴-2B</v>
+      </c>
+      <c r="P23" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46" t="s">
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="T23" s="46" t="s">
+      <c r="T23" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="U23" s="46"/>
-      <c r="V23" s="46"/>
-      <c r="W23" s="46" t="s">
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="X23" s="46"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="46"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
       <c r="L24" s="31" t="s">
         <v>137</v>
       </c>
       <c r="M24" s="33" t="str">
         <f t="array" ref="M24">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M24))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <v>신운기</v>
       </c>
       <c r="N24" s="33" t="str">
         <f t="array" ref="N24">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M24))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>보-1</v>
-      </c>
-      <c r="P24" s="46" t="s">
+        <v>게-1</v>
+      </c>
+      <c r="P24" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="Q24" s="46" t="s">
+      <c r="Q24" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="46" t="s">
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46" t="s">
+      <c r="U24" s="45"/>
+      <c r="V24" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="47" t="s">
+      <c r="A25" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
       <c r="L25" s="31" t="s">
         <v>138</v>
       </c>
@@ -4168,121 +4133,123 @@
       </c>
       <c r="N25" s="33" t="str">
         <f t="array" ref="N25">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M25))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
-      </c>
-      <c r="P25" s="46" t="s">
+        <v>주-5</v>
+      </c>
+      <c r="P25" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46" t="s">
+      <c r="Q25" s="45"/>
+      <c r="R25" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46" t="s">
+      <c r="S25" s="45"/>
+      <c r="T25" s="45"/>
+      <c r="U25" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46" t="s">
+      <c r="V25" s="45"/>
+      <c r="W25" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="X25" s="46"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="46"/>
+      <c r="X25" s="45"/>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="45"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
       <c r="M26" s="33" t="str">
         <f t="array" ref="M26">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
       </c>
       <c r="N26" s="33" t="str">
         <f t="array" ref="N26">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
-      </c>
-      <c r="P26" s="46" t="s">
+        <v>휴-3B</v>
+      </c>
+      <c r="P26" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="45"/>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="45"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
       <c r="M27" s="33" t="str">
         <f t="array" ref="M27">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>신운기</v>
       </c>
       <c r="N27" s="33" t="str">
         <f t="array" ref="N27">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
-      </c>
-      <c r="P27" s="46" t="s">
+        <v>주-3</v>
+      </c>
+      <c r="P27" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="45"/>
+      <c r="U27" s="45"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="X27" s="45"/>
+      <c r="Y27" s="45"/>
+      <c r="Z27" s="45"/>
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="43"/>
+      <c r="B28" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
       <c r="M28" s="33" t="str">
         <f t="array" ref="M28">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M28))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <v>유복현</v>
       </c>
       <c r="N28" s="33" t="str">
         <f t="array" ref="N28">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M28))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
+        <v>주-1</v>
       </c>
       <c r="P28" s="40" t="s">
         <v>59</v>
@@ -4302,25 +4269,23 @@
       <c r="A29" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
       <c r="M29" s="33" t="str">
         <f t="array" ref="M29">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M29))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <v>유복현</v>
       </c>
       <c r="N29" s="33" t="str">
         <f t="array" ref="N29">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M29))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v>휴-1A</v>
       </c>
       <c r="P29" s="40" t="s">
         <v>43</v>
@@ -4340,23 +4305,23 @@
       <c r="A30" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
       <c r="M30" s="33" t="str">
         <f t="array" ref="M30">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M30))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <v>유복현</v>
       </c>
       <c r="N30" s="33" t="str">
         <f t="array" ref="N30">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M30))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <v>휴-2A</v>
       </c>
       <c r="P30" s="40" t="s">
         <v>62</v>
@@ -4375,7 +4340,7 @@
     <row r="31" spans="1:26">
       <c r="B31" s="31">
         <f>COUNTA(B2:B30)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C31" s="31">
         <f t="shared" ref="C31:K31" si="0">COUNTA(C2:C30)</f>
@@ -4383,11 +4348,11 @@
       </c>
       <c r="D31" s="31">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E31" s="31">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" s="31">
         <f t="shared" si="0"/>
@@ -4395,11 +4360,11 @@
       </c>
       <c r="G31" s="31">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H31" s="31">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I31" s="31">
         <f t="shared" si="0"/>
@@ -4419,7 +4384,7 @@
       </c>
       <c r="N31" s="33" t="str">
         <f t="array" ref="N31">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M31))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
+        <v>게-1</v>
       </c>
       <c r="Q31" s="31">
         <f>COUNTA(Q2:Q30)</f>
@@ -4469,18 +4434,18 @@
       </c>
       <c r="N32" s="33" t="str">
         <f t="array" ref="N32">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M32))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <v>주-5</v>
       </c>
     </row>
     <row r="33" spans="5:14">
-      <c r="E33" s="44"/>
+      <c r="E33" s="43"/>
       <c r="M33" s="33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1)/ROWS($A$2:$A$30))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N33" s="33" t="str">
         <f t="array" ref="N33">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <v>휴-3A</v>
       </c>
     </row>
     <row r="34" spans="5:14">
@@ -4490,7 +4455,7 @@
       </c>
       <c r="N34" s="33" t="str">
         <f t="array" ref="N34">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M34))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
+        <v>소-1</v>
       </c>
     </row>
     <row r="35" spans="5:14">
@@ -4500,7 +4465,7 @@
       </c>
       <c r="N35" s="33" t="str">
         <f t="array" ref="N35">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M35))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
+        <v>맘-1</v>
       </c>
     </row>
     <row r="36" spans="5:14">
@@ -4510,7 +4475,7 @@
       </c>
       <c r="N36" s="33" t="str">
         <f t="array" ref="N36">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M36))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <v>G-3</v>
       </c>
     </row>
     <row r="37" spans="5:14">
@@ -4520,7 +4485,7 @@
       </c>
       <c r="N37" s="33" t="str">
         <f t="array" ref="N37">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M37))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
+        <v>푸-1</v>
       </c>
     </row>
     <row r="38" spans="5:14">
@@ -4530,47 +4495,47 @@
       </c>
       <c r="N38" s="33" t="str">
         <f t="array" ref="N38">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M38))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>맘-1</v>
+        <v>주-3</v>
       </c>
     </row>
     <row r="39" spans="5:14">
       <c r="M39" s="33" t="str">
         <f t="array" ref="M39">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M39))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <v>김민겸</v>
       </c>
       <c r="N39" s="33" t="str">
         <f t="array" ref="N39">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M39))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>G-3</v>
+        <v>휴-1B</v>
       </c>
     </row>
     <row r="40" spans="5:14">
       <c r="M40" s="33" t="str">
         <f t="array" ref="M40">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M40))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <v>김민겸</v>
       </c>
       <c r="N40" s="33" t="str">
         <f t="array" ref="N40">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M40))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>푸-1</v>
+        <v>휴-2B</v>
       </c>
     </row>
     <row r="41" spans="5:14">
       <c r="M41" s="33" t="str">
         <f t="array" ref="M41">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M41))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <v>김민겸</v>
       </c>
       <c r="N41" s="33" t="str">
         <f t="array" ref="N41">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M41))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <v>점-1</v>
       </c>
     </row>
     <row r="42" spans="5:14">
       <c r="M42" s="33" t="str">
         <f t="array" ref="M42">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M42))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <v>김민겸</v>
       </c>
       <c r="N42" s="33" t="str">
         <f t="array" ref="N42">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M42))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>보-1</v>
+        <v>휴-3B</v>
       </c>
     </row>
     <row r="43" spans="5:14">
@@ -4580,7 +4545,7 @@
       </c>
       <c r="N43" s="33" t="str">
         <f t="array" ref="N43">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M43))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <v>G-1</v>
       </c>
     </row>
     <row r="44" spans="5:14">
@@ -4590,131 +4555,131 @@
       </c>
       <c r="N44" s="33" t="str">
         <f t="array" ref="N44">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M44))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <v>G-2</v>
       </c>
     </row>
     <row r="45" spans="5:14">
       <c r="M45" s="33" t="str">
         <f t="array" ref="M45">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M45))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>김민겸</v>
+        <v>이동철</v>
       </c>
       <c r="N45" s="33" t="str">
         <f t="array" ref="N45">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M45))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>점-1</v>
+        <v>휴-1A</v>
       </c>
     </row>
     <row r="46" spans="5:14">
       <c r="M46" s="33" t="str">
         <f t="array" ref="M46">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M46))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>김민겸</v>
+        <v>이동철</v>
       </c>
       <c r="N46" s="33" t="str">
         <f t="array" ref="N46">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M46))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v>휴-2A</v>
       </c>
     </row>
     <row r="47" spans="5:14">
       <c r="M47" s="33" t="str">
         <f t="array" ref="M47">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M47))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>김민겸</v>
+        <v>이동철</v>
       </c>
       <c r="N47" s="33" t="str">
         <f t="array" ref="N47">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M47))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>G-1</v>
+        <v>휴-3A</v>
       </c>
     </row>
     <row r="48" spans="5:14">
       <c r="M48" s="33" t="str">
         <f t="array" ref="M48">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M48))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>김민겸</v>
+        <v>여연동</v>
       </c>
       <c r="N48" s="33" t="str">
         <f t="array" ref="N48">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M48))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>G-2</v>
+        <v>휴-1B</v>
       </c>
     </row>
     <row r="49" spans="13:14">
       <c r="M49" s="33" t="str">
         <f t="array" ref="M49">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M49))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>김민겸</v>
+        <v>여연동</v>
       </c>
       <c r="N49" s="33" t="str">
         <f t="array" ref="N49">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M49))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>자-1</v>
+        <v>휴-2B</v>
       </c>
     </row>
     <row r="50" spans="13:14">
       <c r="M50" s="33" t="str">
         <f t="array" ref="M50">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M50))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이동철</v>
+        <v>여연동</v>
       </c>
       <c r="N50" s="33" t="str">
         <f t="array" ref="N50">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M50))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <v>휴-3B</v>
       </c>
     </row>
     <row r="51" spans="13:14">
       <c r="M51" s="33" t="str">
         <f t="array" ref="M51">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M51))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이동철</v>
+        <v>박동원</v>
       </c>
       <c r="N51" s="33" t="str">
         <f t="array" ref="N51">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M51))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <v>휴-1B</v>
       </c>
     </row>
     <row r="52" spans="13:14">
       <c r="M52" s="33" t="str">
         <f t="array" ref="M52">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M52))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이동철</v>
+        <v>박동원</v>
       </c>
       <c r="N52" s="33" t="str">
         <f t="array" ref="N52">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M52))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <v>휴-2B</v>
       </c>
     </row>
     <row r="53" spans="13:14">
       <c r="M53" s="33" t="str">
         <f t="array" ref="M53">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M53))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>여연동</v>
+        <v>박동원</v>
       </c>
       <c r="N53" s="33" t="str">
         <f t="array" ref="N53">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M53))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <v>휴-3C</v>
       </c>
     </row>
     <row r="54" spans="13:14">
       <c r="M54" s="33" t="str">
         <f t="array" ref="M54">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M54))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>여연동</v>
+        <v/>
       </c>
       <c r="N54" s="33" t="str">
         <f t="array" ref="N54">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M54))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="13:14">
       <c r="M55" s="33" t="str">
         <f t="array" ref="M55">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M55))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>여연동</v>
+        <v/>
       </c>
       <c r="N55" s="33" t="str">
         <f t="array" ref="N55">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M55))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="13:14">
       <c r="M56" s="33" t="str">
         <f t="array" ref="M56">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M56))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>박동원</v>
+        <v/>
       </c>
       <c r="N56" s="33" t="str">
         <f t="array" ref="N56">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M56))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/비초소_태스크_리스트.xlsx
+++ b/비초소_태스크_리스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF337068-7C2F-475B-AC88-B325E8F6EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7258083-5989-45F5-9C32-42249C35C610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="25820" windowHeight="15500" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="배치" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="154">
   <si>
     <t>경비원명</t>
   </si>
@@ -236,252 +236,237 @@
   </si>
   <si>
     <t>이근재</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-3C</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴게(자정)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-1B</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-3A</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>보-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주-2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이학근</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>B</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-3B</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-2B</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>자-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체-전일</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체-오전</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체-오후</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체-남</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이춘도</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주-3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>게-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>점-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>소-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-1A</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>휴-2A</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>재-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>유복현</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>신운기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>김민겸</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>정창화</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>박동원</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>이동철</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>여연동</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>분담표</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주-4</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주-5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(11)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(07)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(14)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주차단속(20)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>주차단속(21)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>기준표</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체근무</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대체-임시1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>등-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>등원안내</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>맘-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>맘개방</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>푸-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>푸른개방</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>물-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>물오뚜기</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>청-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대청소</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-2</t>
   </si>
   <si>
     <t>G-2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-3</t>
   </si>
   <si>
     <t>G-3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-소등</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-확인2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>G-확인1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>등-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>맘-1</t>
@@ -494,97 +479,110 @@
   </si>
   <si>
     <t>(07)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(11)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(21)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(14)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(20)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>동→서→북</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(일)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(월),(목)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(개방)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(소등)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>(안내)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>춘</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>근</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>학</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>창</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>운</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>복</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>민</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>동</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>연</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>원</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>북초소</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>주-5</t>
-  </si>
-  <si>
-    <t>휴-3C</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>고-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>월세고지서</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리고지서</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>월-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>관-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>서초소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>주-4</t>
   </si>
 </sst>
 </file>
@@ -596,9 +594,17 @@
     <numFmt numFmtId="177" formatCode="h:mm;@"/>
     <numFmt numFmtId="178" formatCode="yyyy/mm/dd\(aaa\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -884,22 +890,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -916,86 +919,116 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1004,43 +1037,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,9 +1083,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1108,7 +1123,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1214,7 +1229,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1356,7 +1371,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1586,14 +1601,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="25" customWidth="1"/>
@@ -1616,94 +1631,94 @@
     <row r="2" spans="1:6">
       <c r="A2" s="26">
         <f t="shared" ref="A2:A32" si="0">IF(OR(C2="소-1",C2="휴-3B",C2="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="26">
         <f t="shared" si="0"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>37</v>
@@ -1712,10 +1727,10 @@
     <row r="10" spans="1:6">
       <c r="A10" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>38</v>
@@ -1724,399 +1739,399 @@
     <row r="11" spans="1:6">
       <c r="A11" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>153</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="26">
         <f t="shared" si="0"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>42</v>
       </c>
       <c r="F16" s="26">
-        <v>46225</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F20" s="28"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="26">
         <f t="shared" si="0"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F21" s="28"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B22" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="26">
         <f t="shared" si="0"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B27" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="26">
         <f t="shared" si="0"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B32" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="26">
-        <f t="shared" ref="A33:A55" si="1">IF(OR(C33="소-1",C33="휴-3B",C33="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46225</v>
+        <f t="shared" ref="A33:A56" si="1">IF(OR(C33="소-1",C33="휴-3B",C33="휴-3C"),$F$16+1,$F$16)</f>
+        <v>46231</v>
       </c>
       <c r="B33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>153</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B34" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="26">
         <f t="shared" si="1"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B40" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B41" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B42" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="26">
         <f t="shared" ref="A43:A44" si="2">IF(OR(C43="소-1",C43="휴-3B",C43="휴-3C"),$F$16+1,$F$16)</f>
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B43" s="27" t="s">
         <v>22</v>
@@ -2128,150 +2143,126 @@
     <row r="44" spans="1:3">
       <c r="A44" s="26">
         <f t="shared" si="2"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B44" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B45" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B47" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B48" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B50" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="26">
         <f t="shared" si="1"/>
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="26">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B53" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="26">
-        <f t="shared" si="1"/>
-        <v>46226</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="26">
-        <f t="shared" si="1"/>
-        <v>46226</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" s="27" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C51" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2302,16 +2293,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="18">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="51" t="s">
-        <v>78</v>
+      <c r="D2" s="52" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2321,14 +2312,14 @@
       <c r="D3" s="44"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="9" style="22" bestFit="1" customWidth="1"/>
@@ -2361,10 +2352,10 @@
         <v>48</v>
       </c>
       <c r="C2" s="9">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.84722222222222221</v>
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="D2" s="53">
+        <v>0.80208333333333337</v>
       </c>
       <c r="E2" s="12"/>
     </row>
@@ -2376,10 +2367,10 @@
         <v>49</v>
       </c>
       <c r="C3" s="9">
-        <v>0.77152777777777781</v>
+        <v>0.80555555555555558</v>
       </c>
       <c r="D3" s="9">
-        <v>0.79097222222222219</v>
+        <v>0.82638888888888884</v>
       </c>
       <c r="E3" s="12"/>
     </row>
@@ -2391,433 +2382,433 @@
         <v>50</v>
       </c>
       <c r="C4" s="9">
-        <v>0.1875</v>
+        <v>0.21527777777777779</v>
       </c>
       <c r="D4" s="9">
-        <v>0.21875</v>
+        <v>0.23958333333333334</v>
       </c>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>110</v>
+      <c r="A5" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>149</v>
       </c>
       <c r="C5" s="9">
-        <v>0.3611111111111111</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D5" s="9">
-        <v>0.40277777777777779</v>
+        <v>0.66597222222222219</v>
       </c>
       <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>112</v>
+      <c r="A6" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>148</v>
       </c>
       <c r="C6" s="9">
-        <v>0.3125</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D6" s="9">
-        <v>0.31944444444444442</v>
+        <v>0.625</v>
       </c>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="38" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C7" s="9">
-        <v>0.24305555555555555</v>
+        <v>0.3125</v>
       </c>
       <c r="D7" s="9">
-        <v>0.25</v>
+        <v>0.31944444444444442</v>
       </c>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="38" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C8" s="9">
-        <v>0.35416666666666669</v>
+        <v>0.24305555555555555</v>
       </c>
       <c r="D8" s="9">
-        <v>0.36458333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C9" s="9">
-        <v>0.59027777777777779</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="D9" s="9">
-        <v>0.60416666666666663</v>
+        <v>0.36458333333333331</v>
       </c>
       <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="38" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C10" s="9">
-        <v>0.875</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D10" s="9">
-        <v>0.88194444444444442</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>126</v>
-      </c>
       <c r="C11" s="9">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="D11" s="9">
-        <v>6.9444444444444441E-3</v>
+        <v>0.88194444444444442</v>
       </c>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>125</v>
-      </c>
       <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="9">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D13" s="9">
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="E12" s="12"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B14" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <v>0.31944444444444442</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D14" s="9">
         <v>0.34652777777777782</v>
-      </c>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0.47222222222222221</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0.49305555555555558</v>
       </c>
       <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="38" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" s="9">
-        <v>0.59027777777777779</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="D15" s="9">
-        <v>0.61111111111111116</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="38" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="9">
-        <v>0.84722222222222221</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="D16" s="9">
-        <v>0.86805555555555558</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="E16" s="12"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>104</v>
       </c>
       <c r="C17" s="9">
         <v>0.88888888888888884</v>
       </c>
       <c r="D17" s="9">
+        <v>0.91319444444444442</v>
+      </c>
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="D18" s="9">
         <v>0.90972222222222221</v>
-      </c>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0.34722222222222221</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0.38819444444444451</v>
       </c>
       <c r="E18" s="12"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19" s="9">
-        <v>0.63888888888888884</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="D19" s="9">
-        <v>0.66597222222222219</v>
+        <v>0.38819444444444451</v>
       </c>
       <c r="E19" s="12"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20" s="9">
-        <v>0.3888888888888889</v>
+        <v>0.63888888888888884</v>
       </c>
       <c r="D20" s="9">
-        <v>0.41597222222222219</v>
+        <v>0.66597222222222219</v>
       </c>
       <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.49930555555555561</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>8</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0.41597222222222219</v>
+      </c>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="10">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D22" s="10">
-        <v>0.58263888888888893</v>
+        <v>0.49930555555555561</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="10">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D23" s="10">
-        <v>0.70763888888888893</v>
+        <v>0.58263888888888893</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C24" s="10">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D24" s="10">
-        <v>0.74930555555555556</v>
+        <v>0.70763888888888893</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>58</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="C25" s="10">
-        <v>0.91666666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D25" s="10">
-        <v>8.2638888888888887E-2</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>8</v>
+        <v>0.74930555555555556</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B26" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C26" s="10">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D26" s="10">
+        <v>8.2638888888888887E-2</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="10">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D27" s="10">
         <v>0.24930555555555561</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E27" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="23" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B28" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C28" s="10">
         <v>0</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D28" s="10">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E27" s="21"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="9">
-        <v>0.3125</v>
-      </c>
-      <c r="D28" s="9">
-        <v>0.3125</v>
-      </c>
-      <c r="E28" s="12"/>
+      <c r="E28" s="21"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="9">
         <v>0.3125</v>
       </c>
       <c r="D29" s="9">
-        <v>0.81180555555555556</v>
+        <v>0.3125</v>
       </c>
       <c r="E29" s="12"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0.3125</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.81180555555555556</v>
+      </c>
+      <c r="E30" s="12"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C31" s="9">
         <v>0.8125</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D31" s="9">
         <v>0.31180555555555561</v>
-      </c>
-      <c r="E30" s="12"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="10">
-        <v>0.3125</v>
-      </c>
-      <c r="D31" s="10">
-        <v>0.3125</v>
       </c>
       <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>64</v>
@@ -2826,59 +2817,69 @@
         <v>0.3125</v>
       </c>
       <c r="D32" s="10">
-        <v>0.81180555555555556</v>
+        <v>0.3125</v>
       </c>
       <c r="E32" s="12"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>64</v>
       </c>
       <c r="C33" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="D33" s="10">
+        <v>0.81180555555555556</v>
+      </c>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="10">
         <v>0.8125</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D34" s="10">
         <v>0.31180555555555556</v>
       </c>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="38" t="s">
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="10">
+      <c r="B35" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="10">
         <v>0.18402777777777779</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D35" s="10">
         <v>0.21527777777777779</v>
       </c>
-      <c r="E34" s="12"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="23" t="s">
+      <c r="E35" s="12"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B36" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C36" s="10">
         <v>0.3125</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D36" s="10">
         <v>0.75</v>
       </c>
-      <c r="E35" s="12"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36"/>
-      <c r="B36"/>
-      <c r="C36"/>
+      <c r="E36" s="12"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37"/>
@@ -2900,8 +2901,13 @@
       <c r="B40"/>
       <c r="C40"/>
     </row>
+    <row r="41" spans="1:5">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2961,18 +2967,18 @@
         <v>95</v>
       </c>
       <c r="L1" s="50">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="M1" s="33" t="str">
-        <f t="array" ref="M1">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M1))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M1">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M1))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이춘도</v>
       </c>
       <c r="N1" s="33" t="str">
-        <f t="array" ref="N1">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M1))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>연-1</v>
+        <f t="array" ref="N1">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M1))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-1</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P1" s="37" t="s">
         <v>98</v>
@@ -3012,32 +3018,32 @@
       <c r="A2" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="30" t="s">
+        <v>137</v>
+      </c>
       <c r="C2" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D2" s="30"/>
       <c r="E2" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
-        <v>147</v>
-      </c>
+      <c r="G2" s="30"/>
       <c r="H2" s="30"/>
       <c r="I2" s="30"/>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
       <c r="L2" s="48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f t="array" ref="M2">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M2))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <f t="array" ref="M2">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M2))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이춘도</v>
       </c>
       <c r="N2" s="33" t="str">
-        <f t="array" ref="N2">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M2))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
+        <f t="array" ref="N2">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M2))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1A</v>
       </c>
       <c r="P2" s="34" t="s">
         <v>83</v>
@@ -3045,14 +3051,14 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="30"/>
       <c r="S2" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T2" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U2" s="30"/>
       <c r="V2" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W2" s="30"/>
       <c r="X2" s="30"/>
@@ -3063,50 +3069,50 @@
       <c r="A3" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="30"/>
+      <c r="B3" s="30" t="s">
+        <v>137</v>
+      </c>
       <c r="C3" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F3" s="30"/>
-      <c r="G3" s="30" t="s">
-        <v>147</v>
-      </c>
+      <c r="G3" s="30"/>
       <c r="H3" s="30"/>
       <c r="I3" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
       <c r="M3" s="33" t="str">
-        <f t="array" ref="M3">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M3))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <f t="array" ref="M3">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M3))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이춘도</v>
       </c>
       <c r="N3" s="33" t="str">
-        <f t="array" ref="N3">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M3))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <f t="array" ref="N3">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M3))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2A</v>
       </c>
       <c r="P3" s="34" t="s">
         <v>88</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="R3" s="30"/>
       <c r="S3" s="30"/>
       <c r="T3" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U3" s="30"/>
       <c r="V3" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W3" s="30"/>
       <c r="X3" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="Y3" s="30"/>
       <c r="Z3" s="30"/>
@@ -3126,15 +3132,15 @@
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
       <c r="L4" s="48" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M4" s="33" t="str">
-        <f t="array" ref="M4">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M4))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <f t="array" ref="M4">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M4))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이춘도</v>
       </c>
       <c r="N4" s="33" t="str">
-        <f t="array" ref="N4">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M4))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <f t="array" ref="N4">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M4))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3B</v>
       </c>
       <c r="P4" s="29" t="s">
         <v>71</v>
@@ -3142,14 +3148,14 @@
       <c r="Q4" s="30"/>
       <c r="R4" s="30"/>
       <c r="S4" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T4" s="30"/>
       <c r="U4" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W4" s="30"/>
       <c r="X4" s="30"/>
@@ -3161,107 +3167,105 @@
         <v>68</v>
       </c>
       <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="C5" s="30" t="s">
+        <v>138</v>
+      </c>
       <c r="D5" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G5" s="30"/>
       <c r="H5" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I5" s="30"/>
       <c r="J5" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>151</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="K5" s="30"/>
       <c r="M5" s="33" t="str">
-        <f t="array" ref="M5">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M5))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이근재</v>
+        <f t="array" ref="M5">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M5))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이춘도</v>
       </c>
       <c r="N5" s="33" t="str">
-        <f t="array" ref="N5">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M5))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
+        <f t="array" ref="N5">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M5))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-3</v>
       </c>
       <c r="P5" s="29" t="s">
         <v>68</v>
       </c>
       <c r="Q5" s="30"/>
       <c r="R5" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S5" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T5" s="30"/>
       <c r="U5" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V5" s="30"/>
       <c r="W5" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="X5" s="30"/>
       <c r="Y5" s="30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30" t="s">
-        <v>143</v>
-      </c>
+      <c r="B6" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="30"/>
       <c r="D6" s="30"/>
       <c r="E6" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F6" s="30"/>
-      <c r="G6" s="30" t="s">
-        <v>147</v>
-      </c>
+      <c r="G6" s="30"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J6" s="30"/>
       <c r="K6" s="30"/>
       <c r="M6" s="33" t="str">
-        <f t="array" ref="M6">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M6))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M6">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M6))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이근재</v>
       </c>
       <c r="N6" s="33" t="str">
-        <f t="array" ref="N6">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M6))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <f t="array" ref="N6">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M6))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-1</v>
       </c>
       <c r="P6" s="29" t="s">
         <v>89</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="R6" s="30"/>
       <c r="S6" s="30"/>
       <c r="T6" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U6" s="30"/>
       <c r="V6" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W6" s="30"/>
       <c r="X6" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="Y6" s="30"/>
       <c r="Z6" s="30"/>
@@ -3271,57 +3275,57 @@
         <v>76</v>
       </c>
       <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="C7" s="30" t="s">
+        <v>138</v>
+      </c>
       <c r="D7" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I7" s="30"/>
       <c r="J7" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>151</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="K7" s="30"/>
       <c r="M7" s="33" t="str">
-        <f t="array" ref="M7">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M7))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M7">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M7))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이근재</v>
       </c>
       <c r="N7" s="33" t="str">
-        <f t="array" ref="N7">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M7))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
+        <f t="array" ref="N7">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M7))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1A</v>
       </c>
       <c r="P7" s="29" t="s">
         <v>76</v>
       </c>
       <c r="Q7" s="30"/>
       <c r="R7" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S7" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T7" s="30"/>
       <c r="U7" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V7" s="30"/>
       <c r="W7" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="X7" s="30"/>
       <c r="Y7" s="30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -3331,25 +3335,25 @@
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F8" s="30"/>
       <c r="G8" s="30"/>
       <c r="H8" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I8" s="30"/>
       <c r="J8" s="30"/>
       <c r="K8" s="30"/>
       <c r="M8" s="33" t="str">
-        <f t="array" ref="M8">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M8))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <f t="array" ref="M8">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M8))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이근재</v>
       </c>
       <c r="N8" s="33" t="str">
-        <f t="array" ref="N8">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M8))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N8">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M8))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v>휴-1B</v>
       </c>
       <c r="P8" s="29" t="s">
@@ -3357,18 +3361,18 @@
       </c>
       <c r="Q8" s="30"/>
       <c r="R8" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
       <c r="W8" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="X8" s="30"/>
       <c r="Y8" s="30"/>
@@ -3380,44 +3384,44 @@
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="H9" s="30"/>
+        <v>141</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
       <c r="M9" s="33" t="str">
-        <f t="array" ref="M9">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M9))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <f t="array" ref="M9">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M9))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이근재</v>
       </c>
       <c r="N9" s="33" t="str">
-        <f t="array" ref="N9">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M9))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N9">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M9))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v>휴-2B</v>
       </c>
       <c r="P9" s="29" t="s">
         <v>85</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
       <c r="U9" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W9" s="30"/>
       <c r="X9" s="30"/>
@@ -3425,52 +3429,52 @@
       <c r="Z9" s="30"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="29" t="s">
-        <v>100</v>
+      <c r="A10" s="54" t="s">
+        <v>99</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
       <c r="D10" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
       <c r="L10" s="48" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M10" s="33" t="str">
-        <f t="array" ref="M10">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M10))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <f t="array" ref="M10">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M10))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이근재</v>
       </c>
       <c r="N10" s="33" t="str">
-        <f t="array" ref="N10">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M10))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>점-1</v>
+        <f t="array" ref="N10">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M10))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>게-1</v>
       </c>
       <c r="P10" s="29" t="s">
         <v>100</v>
       </c>
       <c r="Q10" s="30"/>
       <c r="R10" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S10" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T10" s="30"/>
       <c r="U10" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W10" s="30"/>
       <c r="X10" s="30"/>
@@ -3483,50 +3487,52 @@
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="30"/>
+        <v>138</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>139</v>
+      </c>
       <c r="E11" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F11" s="30"/>
       <c r="G11" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
       <c r="M11" s="33" t="str">
-        <f t="array" ref="M11">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M11))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이학근</v>
+        <f t="array" ref="M11">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M11))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이근재</v>
       </c>
       <c r="N11" s="33" t="str">
-        <f t="array" ref="N11">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M11))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
+        <f t="array" ref="N11">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M11))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3A</v>
       </c>
       <c r="P11" s="29" t="s">
         <v>69</v>
       </c>
       <c r="Q11" s="30"/>
       <c r="R11" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T11" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U11" s="30"/>
       <c r="V11" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W11" s="30"/>
       <c r="X11" s="30" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="Y11" s="30"/>
       <c r="Z11" s="30"/>
@@ -3544,16 +3550,14 @@
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="30" t="s">
-        <v>151</v>
-      </c>
+      <c r="K12" s="30"/>
       <c r="M12" s="33" t="str">
-        <f t="array" ref="M12">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M12))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M12">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M12))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이학근</v>
       </c>
       <c r="N12" s="33" t="str">
-        <f t="array" ref="N12">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M12))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <f t="array" ref="N12">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M12))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1B</v>
       </c>
       <c r="P12" s="29" t="s">
         <v>66</v>
@@ -3573,54 +3577,56 @@
       <c r="A13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="30"/>
+      <c r="B13" s="30" t="s">
+        <v>137</v>
+      </c>
       <c r="C13" s="30"/>
-      <c r="D13" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I13" s="30"/>
       <c r="J13" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="K13" s="30"/>
+        <v>145</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>146</v>
+      </c>
       <c r="M13" s="33" t="str">
-        <f t="array" ref="M13">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M13))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M13">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M13))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이학근</v>
       </c>
       <c r="N13" s="33" t="str">
-        <f t="array" ref="N13">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M13))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <f t="array" ref="N13">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M13))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2B</v>
       </c>
       <c r="P13" s="29" t="s">
         <v>75</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="R13" s="30"/>
       <c r="S13" s="30"/>
       <c r="T13" s="30"/>
       <c r="U13" s="30" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V13" s="30"/>
       <c r="W13" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="X13" s="30"/>
       <c r="Y13" s="30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -3628,28 +3634,28 @@
         <v>87</v>
       </c>
       <c r="B14" s="30"/>
-      <c r="C14" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30" t="s">
+        <v>139</v>
+      </c>
       <c r="E14" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F14" s="30"/>
       <c r="G14" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
       <c r="M14" s="33" t="str">
-        <f t="array" ref="M14">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M14))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M14">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M14))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이학근</v>
       </c>
       <c r="N14" s="33" t="str">
-        <f t="array" ref="N14">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M14))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>자-1</v>
+        <f t="array" ref="N14">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M14))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>점-1</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>87</v>
@@ -3657,14 +3663,14 @@
       <c r="Q14" s="30"/>
       <c r="R14" s="30"/>
       <c r="S14" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T14" s="30" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U14" s="30"/>
       <c r="V14" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W14" s="30"/>
       <c r="X14" s="30"/>
@@ -3673,42 +3679,39 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
-      <c r="E15" s="30" t="s">
-        <v>145</v>
-      </c>
+      <c r="E15" s="30"/>
       <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="G15" s="30" t="s">
+        <v>142</v>
+      </c>
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
       <c r="K15" s="30"/>
-      <c r="L15" s="31" t="s">
-        <v>141</v>
-      </c>
       <c r="M15" s="33" t="str">
-        <f t="array" ref="M15">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M15))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <f t="array" ref="M15">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M15))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이학근</v>
       </c>
       <c r="N15" s="33" t="str">
-        <f t="array" ref="N15">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M15))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
+        <f t="array" ref="N15">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M15))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-4</v>
       </c>
       <c r="P15" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q15" s="30"/>
       <c r="R15" s="30"/>
       <c r="S15" s="30"/>
-      <c r="T15" s="30" t="s">
-        <v>145</v>
-      </c>
+      <c r="T15" s="30"/>
       <c r="U15" s="30"/>
-      <c r="V15" s="30"/>
+      <c r="V15" s="30" t="s">
+        <v>142</v>
+      </c>
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
       <c r="Y15" s="30"/>
@@ -3716,47 +3719,47 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="29" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="H16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
       <c r="M16" s="33" t="str">
-        <f t="array" ref="M16">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M16))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <f t="array" ref="M16">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M16))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이학근</v>
       </c>
       <c r="N16" s="33" t="str">
-        <f t="array" ref="N16">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M16))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <f t="array" ref="N16">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M16))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3A</v>
       </c>
       <c r="P16" s="29" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q16" s="30"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="30"/>
       <c r="U16" s="30"/>
-      <c r="V16" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="W16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30" t="s">
+        <v>143</v>
+      </c>
       <c r="X16" s="30"/>
       <c r="Y16" s="30"/>
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
@@ -3765,21 +3768,21 @@
       <c r="F17" s="30"/>
       <c r="G17" s="30"/>
       <c r="H17" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
       <c r="M17" s="33" t="str">
-        <f t="array" ref="M17">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M17))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <f t="array" ref="M17">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M17))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이학근</v>
       </c>
       <c r="N17" s="33" t="str">
-        <f t="array" ref="N17">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M17))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <f t="array" ref="N17">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M17))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>소-1</v>
       </c>
       <c r="P17" s="29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q17" s="30"/>
       <c r="R17" s="30"/>
@@ -3788,7 +3791,7 @@
       <c r="U17" s="30"/>
       <c r="V17" s="30"/>
       <c r="W17" s="30" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="X17" s="30"/>
       <c r="Y17" s="30"/>
@@ -3796,47 +3799,50 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
       <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30" t="s">
-        <v>148</v>
-      </c>
+      <c r="G18" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18" s="30"/>
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
+      <c r="L18" s="31" t="s">
+        <v>136</v>
+      </c>
       <c r="M18" s="33" t="str">
-        <f t="array" ref="M18">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M18))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>정창화</v>
+        <f t="array" ref="M18">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M18))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이학근</v>
       </c>
       <c r="N18" s="33" t="str">
-        <f t="array" ref="N18">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M18))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>점-1</v>
+        <f t="array" ref="N18">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M18))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-3</v>
       </c>
       <c r="P18" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q18" s="30"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="30"/>
       <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30" t="s">
-        <v>148</v>
-      </c>
+      <c r="V18" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="W18" s="30"/>
       <c r="X18" s="30"/>
       <c r="Y18" s="30"/>
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="29" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -3844,25 +3850,25 @@
       <c r="E19" s="30"/>
       <c r="F19" s="30"/>
       <c r="G19" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H19" s="30"/>
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
       <c r="L19" s="31" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M19" s="33" t="str">
-        <f t="array" ref="M19">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M19))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M19">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M19))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>정창화</v>
       </c>
       <c r="N19" s="33" t="str">
-        <f t="array" ref="N19">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M19))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <f t="array" ref="N19">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M19))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-1</v>
       </c>
       <c r="P19" s="29" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="Q19" s="30"/>
       <c r="R19" s="30"/>
@@ -3870,7 +3876,7 @@
       <c r="T19" s="30"/>
       <c r="U19" s="30"/>
       <c r="V19" s="30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W19" s="30"/>
       <c r="X19" s="30"/>
@@ -3878,93 +3884,97 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="31" t="s">
+      <c r="A20" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45" t="s">
         <v>139</v>
       </c>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="48" t="s">
+        <v>130</v>
+      </c>
       <c r="M20" s="33" t="str">
-        <f t="array" ref="M20">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M20))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M20">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M20))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>정창화</v>
       </c>
       <c r="N20" s="33" t="str">
-        <f t="array" ref="N20">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M20))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
-      </c>
-      <c r="P20" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
+        <f t="array" ref="N20">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M20))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1A</v>
+      </c>
+      <c r="P20" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="45"/>
+      <c r="U20" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="V20" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="W20" s="45"/>
+      <c r="X20" s="45"/>
+      <c r="Y20" s="45"/>
+      <c r="Z20" s="45"/>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="46" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
-      <c r="D21" s="45" t="s">
-        <v>144</v>
-      </c>
+      <c r="D21" s="45"/>
       <c r="E21" s="45"/>
-      <c r="F21" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="45" t="s">
-        <v>147</v>
-      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="45"/>
       <c r="I21" s="45"/>
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
       <c r="L21" s="48" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="array" ref="M21">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M21))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M21">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M21))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>정창화</v>
       </c>
       <c r="N21" s="33" t="str">
-        <f t="array" ref="N21">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M21))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>등-1</v>
+        <f t="array" ref="N21">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M21))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2A</v>
       </c>
       <c r="P21" s="45" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
+      <c r="R21" s="45" t="s">
+        <v>138</v>
+      </c>
       <c r="S21" s="45" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="T21" s="45"/>
       <c r="U21" s="45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="V21" s="45" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="W21" s="45"/>
       <c r="X21" s="45"/>
@@ -3973,7 +3983,7 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="46" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -3981,52 +3991,50 @@
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
       <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
+      <c r="H22" s="45" t="s">
+        <v>143</v>
+      </c>
       <c r="I22" s="45"/>
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
-      <c r="L22" s="48" t="s">
-        <v>135</v>
+      <c r="L22" s="31" t="s">
+        <v>132</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="array" ref="M22">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M22))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <f t="array" ref="M22">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M22))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>정창화</v>
       </c>
       <c r="N22" s="33" t="str">
-        <f t="array" ref="N22">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M22))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <f t="array" ref="N22">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M22))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>점-1</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="45"/>
-      <c r="R22" s="45" t="s">
+      <c r="R22" s="45"/>
+      <c r="S22" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="T22" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="U22" s="45"/>
+      <c r="V22" s="45"/>
+      <c r="W22" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="S22" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="T22" s="45"/>
-      <c r="U22" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="V22" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="W22" s="45"/>
       <c r="X22" s="45"/>
       <c r="Y22" s="45"/>
       <c r="Z22" s="45"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="46" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
-      <c r="D23" s="45" t="s">
-        <v>144</v>
-      </c>
+      <c r="D23" s="45"/>
       <c r="E23" s="45"/>
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
@@ -4035,39 +4043,39 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
       <c r="L23" s="31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="array" ref="M23">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M23))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <f t="array" ref="M23">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M23))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>정창화</v>
       </c>
       <c r="N23" s="33" t="str">
-        <f t="array" ref="N23">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M23))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <f t="array" ref="N23">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M23))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3A</v>
       </c>
       <c r="P23" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q23" s="45"/>
+        <v>70</v>
+      </c>
+      <c r="Q23" s="45" t="s">
+        <v>137</v>
+      </c>
       <c r="R23" s="45"/>
-      <c r="S23" s="45" t="s">
-        <v>144</v>
-      </c>
+      <c r="S23" s="45"/>
       <c r="T23" s="45" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45" t="s">
-        <v>148</v>
-      </c>
+      <c r="V23" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="W23" s="45"/>
       <c r="X23" s="45"/>
       <c r="Y23" s="45"/>
       <c r="Z23" s="45"/>
     </row>
     <row r="24" spans="1:26">
       <c r="A24" s="46" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B24" s="45"/>
       <c r="C24" s="45"/>
@@ -4080,39 +4088,39 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
       <c r="L24" s="31" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="array" ref="M24">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M24))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>신운기</v>
+        <f t="array" ref="M24">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M24))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>정창화</v>
       </c>
       <c r="N24" s="33" t="str">
-        <f t="array" ref="N24">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M24))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
+        <f t="array" ref="N24">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M24))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>소-1</v>
       </c>
       <c r="P24" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q24" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="R24" s="45"/>
+        <v>90</v>
+      </c>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="45" t="s">
+        <v>138</v>
+      </c>
       <c r="S24" s="45"/>
-      <c r="T24" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="U24" s="45"/>
-      <c r="V24" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="W24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45" t="s">
+        <v>143</v>
+      </c>
       <c r="X24" s="45"/>
       <c r="Y24" s="45"/>
       <c r="Z24" s="45"/>
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="46" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -4124,40 +4132,31 @@
       <c r="I25" s="45"/>
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
-      <c r="L25" s="31" t="s">
-        <v>138</v>
-      </c>
       <c r="M25" s="33" t="str">
-        <f t="array" ref="M25">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M25))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M25">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M25))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>신운기</v>
       </c>
       <c r="N25" s="33" t="str">
-        <f t="array" ref="N25">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M25))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
-      </c>
-      <c r="P25" s="45" t="s">
-        <v>90</v>
+        <f t="array" ref="N25">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M25))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1B</v>
+      </c>
+      <c r="P25" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="Q25" s="45"/>
-      <c r="R25" s="45" t="s">
-        <v>143</v>
-      </c>
+      <c r="R25" s="45"/>
       <c r="S25" s="45"/>
       <c r="T25" s="45"/>
-      <c r="U25" s="45" t="s">
-        <v>146</v>
-      </c>
+      <c r="U25" s="45"/>
       <c r="V25" s="45"/>
-      <c r="W25" s="45" t="s">
-        <v>148</v>
-      </c>
+      <c r="W25" s="45"/>
       <c r="X25" s="45"/>
       <c r="Y25" s="45"/>
       <c r="Z25" s="45"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="45" t="s">
-        <v>117</v>
+      <c r="A26" s="46" t="s">
+        <v>150</v>
       </c>
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
@@ -4170,15 +4169,15 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
       <c r="M26" s="33" t="str">
-        <f t="array" ref="M26">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M26">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M26))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>신운기</v>
       </c>
       <c r="N26" s="33" t="str">
-        <f t="array" ref="N26">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M26))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
-      </c>
-      <c r="P26" s="45" t="s">
-        <v>117</v>
+        <f t="array" ref="N26">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M26))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2B</v>
+      </c>
+      <c r="P26" s="46" t="s">
+        <v>150</v>
       </c>
       <c r="Q26" s="45"/>
       <c r="R26" s="45"/>
@@ -4193,7 +4192,7 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="45"/>
       <c r="C27" s="45"/>
@@ -4206,15 +4205,15 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
       <c r="M27" s="33" t="str">
-        <f t="array" ref="M27">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M27">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M27))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>신운기</v>
       </c>
       <c r="N27" s="33" t="str">
-        <f t="array" ref="N27">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M27))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <f t="array" ref="N27">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M27))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>게-1</v>
       </c>
       <c r="P27" s="45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q27" s="45"/>
       <c r="R27" s="45"/>
@@ -4228,46 +4227,44 @@
       <c r="Z27" s="45"/>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
+      <c r="A28" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
       <c r="M28" s="33" t="str">
-        <f t="array" ref="M28">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M28))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <f t="array" ref="M28">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M28))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>신운기</v>
       </c>
       <c r="N28" s="33" t="str">
-        <f t="array" ref="N28">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M28))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-1</v>
-      </c>
-      <c r="P28" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
+        <f t="array" ref="N28">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M28))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-4</v>
+      </c>
+      <c r="P28" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="45"/>
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="40" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="42"/>
@@ -4280,15 +4277,15 @@
       <c r="J29" s="42"/>
       <c r="K29" s="42"/>
       <c r="M29" s="33" t="str">
-        <f t="array" ref="M29">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M29))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <f t="array" ref="M29">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M29))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>신운기</v>
       </c>
       <c r="N29" s="33" t="str">
-        <f t="array" ref="N29">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M29))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <f t="array" ref="N29">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M29))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3B</v>
       </c>
       <c r="P29" s="40" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="Q29" s="41"/>
       <c r="R29" s="41"/>
@@ -4303,28 +4300,30 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="40" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="42"/>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
       <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="42" t="s">
+        <v>142</v>
+      </c>
       <c r="H30" s="42"/>
       <c r="I30" s="42"/>
       <c r="J30" s="42"/>
       <c r="K30" s="42"/>
       <c r="M30" s="33" t="str">
-        <f t="array" ref="M30">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M30))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <f t="array" ref="M30">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M30))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>신운기</v>
       </c>
       <c r="N30" s="33" t="str">
-        <f t="array" ref="N30">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M30))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <f t="array" ref="N30">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M30))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-3</v>
       </c>
       <c r="P30" s="40" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="Q30" s="41"/>
       <c r="R30" s="41"/>
@@ -4338,348 +4337,374 @@
       <c r="Z30" s="41"/>
     </row>
     <row r="31" spans="1:26">
-      <c r="B31" s="31">
-        <f>COUNTA(B2:B30)</f>
-        <v>1</v>
-      </c>
-      <c r="C31" s="31">
-        <f t="shared" ref="C31:K31" si="0">COUNTA(C2:C30)</f>
+      <c r="A31" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="M31" s="33" t="str">
+        <f t="array" ref="M31">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M31))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>유복현</v>
+      </c>
+      <c r="N31" s="33" t="str">
+        <f t="array" ref="N31">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M31))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>주-4</v>
+      </c>
+      <c r="P31" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
+      <c r="W31" s="41"/>
+      <c r="X31" s="41"/>
+      <c r="Y31" s="41"/>
+      <c r="Z31" s="41"/>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="B32" s="31">
+        <f t="shared" ref="B32:K32" si="0">COUNTA(B2:B31)</f>
+        <v>5</v>
+      </c>
+      <c r="C32" s="31">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D32" s="31">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E32" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F32" s="31">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G32" s="31">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="31">
+      <c r="H32" s="31">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G31" s="31">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="H31" s="31">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I31" s="31">
+        <v>8</v>
+      </c>
+      <c r="I32" s="31">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J32" s="31">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K32" s="31">
         <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M32" s="33" t="str">
+        <f t="array" ref="M32">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M32))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>유복현</v>
+      </c>
+      <c r="N32" s="33" t="str">
+        <f t="array" ref="N32">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M32))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3A</v>
+      </c>
+      <c r="Q32" s="31">
+        <f t="shared" ref="Q32:Z32" si="1">COUNTA(Q2:Q31)</f>
+        <v>5</v>
+      </c>
+      <c r="R32" s="31">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="S32" s="31">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T32" s="31">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="U32" s="31">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="V32" s="31">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="W32" s="31">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="X32" s="31">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="M31" s="33" t="str">
-        <f t="array" ref="M31">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M31))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
-      </c>
-      <c r="N31" s="33" t="str">
-        <f t="array" ref="N31">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M31))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>게-1</v>
-      </c>
-      <c r="Q31" s="31">
-        <f>COUNTA(Q2:Q30)</f>
-        <v>5</v>
-      </c>
-      <c r="R31" s="31">
-        <f t="shared" ref="R31" si="1">COUNTA(R2:R30)</f>
-        <v>8</v>
-      </c>
-      <c r="S31" s="31">
-        <f t="shared" ref="S31" si="2">COUNTA(S2:S30)</f>
-        <v>11</v>
-      </c>
-      <c r="T31" s="31">
-        <f t="shared" ref="T31" si="3">COUNTA(T2:T30)</f>
-        <v>9</v>
-      </c>
-      <c r="U31" s="31">
-        <f t="shared" ref="U31" si="4">COUNTA(U2:U30)</f>
-        <v>9</v>
-      </c>
-      <c r="V31" s="31">
-        <f t="shared" ref="V31" si="5">COUNTA(V2:V30)</f>
-        <v>14</v>
-      </c>
-      <c r="W31" s="31">
-        <f t="shared" ref="W31" si="6">COUNTA(W2:W30)</f>
-        <v>8</v>
-      </c>
-      <c r="X31" s="31">
-        <f t="shared" ref="X31" si="7">COUNTA(X2:X30)</f>
+      <c r="Y32" s="31">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="Y31" s="31">
-        <f t="shared" ref="Y31" si="8">COUNTA(Y2:Y30)</f>
+      <c r="Z32" s="31">
+        <f t="shared" si="1"/>
         <v>3</v>
-      </c>
-      <c r="Z31" s="31">
-        <f t="shared" ref="Z31" si="9">COUNTA(Z2:Z30)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26">
-      <c r="M32" s="33" t="str">
-        <f t="array" ref="M32">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M32))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
-      </c>
-      <c r="N32" s="33" t="str">
-        <f t="array" ref="N32">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M32))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-5</v>
       </c>
     </row>
     <row r="33" spans="5:14">
       <c r="E33" s="43"/>
       <c r="M33" s="33" t="str">
-        <f t="array" ref="M33">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M33">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M33))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N33" s="33" t="str">
-        <f t="array" ref="N33">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M33))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <f t="array" ref="N33">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M33))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>소-1</v>
       </c>
     </row>
     <row r="34" spans="5:14">
       <c r="M34" s="33" t="str">
-        <f t="array" ref="M34">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M34))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M34">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M34))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N34" s="33" t="str">
-        <f t="array" ref="N34">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M34))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>소-1</v>
+        <f t="array" ref="N34">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M34))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>맘-1</v>
       </c>
     </row>
     <row r="35" spans="5:14">
       <c r="M35" s="33" t="str">
-        <f t="array" ref="M35">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M35))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M35">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M35))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N35" s="33" t="str">
-        <f t="array" ref="N35">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M35))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>맘-1</v>
+        <f t="array" ref="N35">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M35))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>G-3</v>
       </c>
     </row>
     <row r="36" spans="5:14">
       <c r="M36" s="33" t="str">
-        <f t="array" ref="M36">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M36))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M36">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M36))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N36" s="33" t="str">
-        <f t="array" ref="N36">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M36))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>G-3</v>
+        <f t="array" ref="N36">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M36))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>푸-1</v>
       </c>
     </row>
     <row r="37" spans="5:14">
       <c r="M37" s="33" t="str">
-        <f t="array" ref="M37">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M37))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M37">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M37))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>유복현</v>
       </c>
       <c r="N37" s="33" t="str">
-        <f t="array" ref="N37">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M37))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>푸-1</v>
+        <f t="array" ref="N37">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M37))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>연-2</v>
       </c>
     </row>
     <row r="38" spans="5:14">
       <c r="M38" s="33" t="str">
-        <f t="array" ref="M38">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M38))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>유복현</v>
+        <f t="array" ref="M38">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M38))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>김민겸</v>
       </c>
       <c r="N38" s="33" t="str">
-        <f t="array" ref="N38">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M38))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>주-3</v>
+        <f t="array" ref="N38">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M38))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1B</v>
       </c>
     </row>
     <row r="39" spans="5:14">
       <c r="M39" s="33" t="str">
-        <f t="array" ref="M39">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M39))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M39">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M39))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N39" s="33" t="str">
-        <f t="array" ref="N39">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M39))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <f t="array" ref="N39">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M39))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2B</v>
       </c>
     </row>
     <row r="40" spans="5:14">
       <c r="M40" s="33" t="str">
-        <f t="array" ref="M40">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M40))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M40">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M40))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N40" s="33" t="str">
-        <f t="array" ref="N40">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M40))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <f t="array" ref="N40">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M40))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>점-1</v>
       </c>
     </row>
     <row r="41" spans="5:14">
       <c r="M41" s="33" t="str">
-        <f t="array" ref="M41">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M41))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M41">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M41))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N41" s="33" t="str">
-        <f t="array" ref="N41">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M41))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>점-1</v>
+        <f t="array" ref="N41">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M41))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>게-1</v>
       </c>
     </row>
     <row r="42" spans="5:14">
       <c r="M42" s="33" t="str">
-        <f t="array" ref="M42">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M42))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M42">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M42))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N42" s="33" t="str">
-        <f t="array" ref="N42">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M42))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N42">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M42))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v>휴-3B</v>
       </c>
     </row>
     <row r="43" spans="5:14">
       <c r="M43" s="33" t="str">
-        <f t="array" ref="M43">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M43))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M43">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M43))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N43" s="33" t="str">
-        <f t="array" ref="N43">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M43))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N43">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M43))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v>G-1</v>
       </c>
     </row>
     <row r="44" spans="5:14">
       <c r="M44" s="33" t="str">
-        <f t="array" ref="M44">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M44))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M44">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M44))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>김민겸</v>
       </c>
       <c r="N44" s="33" t="str">
-        <f t="array" ref="N44">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M44))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N44">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M44))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v>G-2</v>
       </c>
     </row>
     <row r="45" spans="5:14">
       <c r="M45" s="33" t="str">
-        <f t="array" ref="M45">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M45))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>이동철</v>
+        <f t="array" ref="M45">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M45))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>김민겸</v>
       </c>
       <c r="N45" s="33" t="str">
-        <f t="array" ref="N45">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M45))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1A</v>
+        <f t="array" ref="N45">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M45))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>자-1</v>
       </c>
     </row>
     <row r="46" spans="5:14">
       <c r="M46" s="33" t="str">
-        <f t="array" ref="M46">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M46))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M46">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M46))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이동철</v>
       </c>
       <c r="N46" s="33" t="str">
-        <f t="array" ref="N46">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M46))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2A</v>
+        <f t="array" ref="N46">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M46))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1A</v>
       </c>
     </row>
     <row r="47" spans="5:14">
       <c r="M47" s="33" t="str">
-        <f t="array" ref="M47">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M47))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M47">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M47))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>이동철</v>
       </c>
       <c r="N47" s="33" t="str">
-        <f t="array" ref="N47">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M47))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3A</v>
+        <f t="array" ref="N47">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M47))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2A</v>
       </c>
     </row>
     <row r="48" spans="5:14">
       <c r="M48" s="33" t="str">
-        <f t="array" ref="M48">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M48))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>여연동</v>
+        <f t="array" ref="M48">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M48))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>이동철</v>
       </c>
       <c r="N48" s="33" t="str">
-        <f t="array" ref="N48">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M48))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <f t="array" ref="N48">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M48))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3A</v>
       </c>
     </row>
     <row r="49" spans="13:14">
       <c r="M49" s="33" t="str">
-        <f t="array" ref="M49">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M49))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M49">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M49))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>여연동</v>
       </c>
       <c r="N49" s="33" t="str">
-        <f t="array" ref="N49">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M49))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <f t="array" ref="N49">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M49))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-1B</v>
       </c>
     </row>
     <row r="50" spans="13:14">
       <c r="M50" s="33" t="str">
-        <f t="array" ref="M50">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M50))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M50">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M50))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>여연동</v>
       </c>
       <c r="N50" s="33" t="str">
-        <f t="array" ref="N50">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M50))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3B</v>
+        <f t="array" ref="N50">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M50))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-2B</v>
       </c>
     </row>
     <row r="51" spans="13:14">
       <c r="M51" s="33" t="str">
-        <f t="array" ref="M51">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M51))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>박동원</v>
+        <f t="array" ref="M51">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M51))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v>여연동</v>
       </c>
       <c r="N51" s="33" t="str">
-        <f t="array" ref="N51">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M51))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-1B</v>
+        <f t="array" ref="N51">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M51))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3B</v>
       </c>
     </row>
     <row r="52" spans="13:14">
       <c r="M52" s="33" t="str">
-        <f t="array" ref="M52">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M52))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M52">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M52))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v>박동원</v>
       </c>
       <c r="N52" s="33" t="str">
-        <f t="array" ref="N52">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M52))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-2B</v>
+        <f t="array" ref="N52">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M52))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v>휴-3B</v>
       </c>
     </row>
     <row r="53" spans="13:14">
       <c r="M53" s="33" t="str">
-        <f t="array" ref="M53">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M53))-1)/ROWS($A$2:$A$30))+1),"")</f>
-        <v>박동원</v>
+        <f t="array" ref="M53">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M53))-1)/ROWS($A$2:$A$31))+1),"")</f>
+        <v/>
       </c>
       <c r="N53" s="33" t="str">
-        <f t="array" ref="N53">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M53))-1,ROWS($A$2:$A$30))+1),"")</f>
-        <v>휴-3C</v>
+        <f t="array" ref="N53">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M53))-1,ROWS($A$2:$A$31))+1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="54" spans="13:14">
       <c r="M54" s="33" t="str">
-        <f t="array" ref="M54">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M54))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M54">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M54))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
       <c r="N54" s="33" t="str">
-        <f t="array" ref="N54">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M54))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N54">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M54))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="55" spans="13:14">
       <c r="M55" s="33" t="str">
-        <f t="array" ref="M55">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M55))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M55">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M55))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
       <c r="N55" s="33" t="str">
-        <f t="array" ref="N55">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M55))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N55">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M55))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
     </row>
     <row r="56" spans="13:14">
       <c r="M56" s="33" t="str">
-        <f t="array" ref="M56">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M56))-1)/ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="M56">IFERROR(INDEX($B$1:$K$1,INT((SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M56))-1)/ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
       <c r="N56" s="33" t="str">
-        <f t="array" ref="N56">IFERROR(INDEX($A$2:$A$30,MOD(SMALL(IF($B$2:$K$30&lt;&gt;"",(COLUMN($B$2:$K$30)-COLUMN($B$2))*ROWS($A$2:$A$30)+ROW($B$2:$K$30)-ROW($B$2)+1),ROWS($M$1:M56))-1,ROWS($A$2:$A$30))+1),"")</f>
+        <f t="array" ref="N56">IFERROR(INDEX($A$2:$A$31,MOD(SMALL(IF($B$2:$K$31&lt;&gt;"",(COLUMN($B$2:$K$31)-COLUMN($B$2))*ROWS($A$2:$A$31)+ROW($B$2:$K$31)-ROW($B$2)+1),ROWS($M$1:M56))-1,ROWS($A$2:$A$31))+1),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
